--- a/Assets/StreamingAssets/PathTable.xlsx
+++ b/Assets/StreamingAssets/PathTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="path" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     </r>
   </si>
   <si>
-    <t>192.168.1.154</t>
+    <t>8.133.179.78</t>
   </si>
   <si>
     <r>
@@ -128,13 +128,13 @@
     <t>批量上传</t>
   </si>
   <si>
-    <t>http://192.168.1.154/VRTMP/PhpLogic/UploadFiles.php</t>
+    <t>http://8.133.179.78/VRTMP/PhpLogic/UploadFiles.php</t>
   </si>
   <si>
     <t>删除文件</t>
   </si>
   <si>
-    <t>http://192.168.1.154/VRTMP/PhpLogic/DeleteFile.php</t>
+    <t>http://8.133.179.78/VRTMP/PhpLogic/DeleteFile.php</t>
   </si>
   <si>
     <t>工单及操作步骤存放地址</t>
@@ -146,13 +146,13 @@
     <t>创建软件缩略图文件夹</t>
   </si>
   <si>
-    <t>http://192.168.1.154/VRTMP/PhpLogic/CreatesoftWareTxtureFolder.php</t>
+    <t>http://8.133.179.78/VRTMP/PhpLogic/CreatesoftWareTxtureFolder.php</t>
   </si>
   <si>
     <t>删除软件缩略图文件夹</t>
   </si>
   <si>
-    <t>http://192.168.1.154/VRTMP/PhpLogic/DeletesoftWareTxtureFolder.php</t>
+    <t>http://8.133.179.78/VRTMP/PhpLogic/DeletesoftWareTxtureFolder.php</t>
   </si>
 </sst>
 </file>
@@ -1498,8 +1498,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" display="https://account.huaweicloud.com/obmgr/invitation/invitation.html?id=b9e166d8-a94a-4f9f-b997-9e34ebfffdce"/>
-    <hyperlink ref="C9" r:id="rId2" display="http://192.168.1.154/VRTMP/PhpLogic/UploadFiles.php" tooltip="http://192.168.1.154/VRTMP/PhpLogic/UploadFiles.php"/>
-    <hyperlink ref="C10" r:id="rId3" display="http://192.168.1.154/VRTMP/PhpLogic/DeleteFile.php" tooltip="http://192.168.1.154/VRTMP/PhpLogic/DeleteFile.php"/>
+    <hyperlink ref="C9" r:id="rId2" display="http://8.133.179.78/VRTMP/PhpLogic/UploadFiles.php" tooltip="http://192.168.1.154/VRTMP/PhpLogic/UploadFiles.php"/>
+    <hyperlink ref="C10" r:id="rId3" display="http://8.133.179.78/VRTMP/PhpLogic/DeleteFile.php" tooltip="http://192.168.1.154/VRTMP/PhpLogic/DeleteFile.php"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
